--- a/import_RT_converted.xlsx
+++ b/import_RT_converted.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trenaldyikkyuarifin/Documents/Project WEB/ahcc-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59635F75-5375-1143-BE3A-EB3CBB4F1AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A607277-6750-BD42-AD86-53530FB7F934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1180" windowWidth="27640" windowHeight="16820" xr2:uid="{7AB2FFD0-AE47-0442-A66D-1B55ACEA1D26}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2333" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="594">
   <si>
     <t>no_rm</t>
   </si>
@@ -1749,6 +1749,75 @@
   </si>
   <si>
     <t>Khoe Pao Thing, Ny</t>
+  </si>
+  <si>
+    <t>Wiwik Wahyuni, Ny</t>
+  </si>
+  <si>
+    <t>Ca Ear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mimik Idayana, Ny </t>
+  </si>
+  <si>
+    <t>Pipit Puspita Ningrum</t>
+  </si>
+  <si>
+    <t>Ependimoma</t>
+  </si>
+  <si>
+    <t>Maria Ulfah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liana Fenawati, Ny </t>
+  </si>
+  <si>
+    <t>Tjauw, Lilis Handayani, Ny</t>
+  </si>
+  <si>
+    <t>Haris Fadillah, Tn</t>
+  </si>
+  <si>
+    <t>Yurike Florensia Linarwan, Nn</t>
+  </si>
+  <si>
+    <t>Mathuri,Tn</t>
+  </si>
+  <si>
+    <t>Kho Tian Hu, Tn</t>
+  </si>
+  <si>
+    <t>Jie Wen Jong</t>
+  </si>
+  <si>
+    <t>Sugiharto, Tn</t>
+  </si>
+  <si>
+    <t>Astrocytoma</t>
+  </si>
+  <si>
+    <t>Dyah Puspita Sari</t>
+  </si>
+  <si>
+    <t>Mariatoen Elly Kartikasari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lila Tri Ermanova, Ny </t>
+  </si>
+  <si>
+    <t>Maria Odilia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wahyuning Raudiyah Maryama, Ny </t>
+  </si>
+  <si>
+    <t>Tatik Nariasih</t>
+  </si>
+  <si>
+    <t>Hotini</t>
+  </si>
+  <si>
+    <t>Eny Yustanti, Ny</t>
   </si>
 </sst>
 </file>
@@ -2121,7 +2190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D53FD7-D959-3E41-AFEE-851F0F46DDFE}">
-  <dimension ref="A1:G469"/>
+  <dimension ref="A1:G489"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -12911,6 +12980,466 @@
         <v>33</v>
       </c>
     </row>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A470">
+        <v>424414</v>
+      </c>
+      <c r="B470" s="1">
+        <v>46027</v>
+      </c>
+      <c r="C470" t="s">
+        <v>571</v>
+      </c>
+      <c r="D470" t="s">
+        <v>572</v>
+      </c>
+      <c r="E470" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F470" t="s">
+        <v>18</v>
+      </c>
+      <c r="G470" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A471">
+        <v>427689</v>
+      </c>
+      <c r="B471" s="1">
+        <v>46027</v>
+      </c>
+      <c r="C471" t="s">
+        <v>573</v>
+      </c>
+      <c r="D471" t="s">
+        <v>48</v>
+      </c>
+      <c r="E471" t="s">
+        <v>39</v>
+      </c>
+      <c r="F471" t="s">
+        <v>18</v>
+      </c>
+      <c r="G471" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A472">
+        <v>428094</v>
+      </c>
+      <c r="B472" s="1">
+        <v>46030</v>
+      </c>
+      <c r="C472" t="s">
+        <v>574</v>
+      </c>
+      <c r="D472" t="s">
+        <v>575</v>
+      </c>
+      <c r="E472" t="s">
+        <v>51</v>
+      </c>
+      <c r="F472" t="s">
+        <v>18</v>
+      </c>
+      <c r="G472" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A473">
+        <v>427971</v>
+      </c>
+      <c r="B473" s="1">
+        <v>46034</v>
+      </c>
+      <c r="C473" t="s">
+        <v>576</v>
+      </c>
+      <c r="D473" t="s">
+        <v>48</v>
+      </c>
+      <c r="E473" t="s">
+        <v>39</v>
+      </c>
+      <c r="F473" t="s">
+        <v>10</v>
+      </c>
+      <c r="G473" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A474">
+        <v>428104</v>
+      </c>
+      <c r="B474" s="1">
+        <v>46034</v>
+      </c>
+      <c r="C474" t="s">
+        <v>577</v>
+      </c>
+      <c r="D474" t="s">
+        <v>50</v>
+      </c>
+      <c r="E474" t="s">
+        <v>51</v>
+      </c>
+      <c r="F474" t="s">
+        <v>14</v>
+      </c>
+      <c r="G474" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A475">
+        <v>318284</v>
+      </c>
+      <c r="B475" s="1">
+        <v>46035</v>
+      </c>
+      <c r="C475" t="s">
+        <v>578</v>
+      </c>
+      <c r="D475" t="s">
+        <v>38</v>
+      </c>
+      <c r="E475" t="s">
+        <v>39</v>
+      </c>
+      <c r="F475" t="s">
+        <v>46</v>
+      </c>
+      <c r="G475" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A476">
+        <v>428046</v>
+      </c>
+      <c r="B476" s="1">
+        <v>46037</v>
+      </c>
+      <c r="C476" t="s">
+        <v>579</v>
+      </c>
+      <c r="D476" t="s">
+        <v>16</v>
+      </c>
+      <c r="E476" t="s">
+        <v>17</v>
+      </c>
+      <c r="F476" t="s">
+        <v>10</v>
+      </c>
+      <c r="G476" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A477">
+        <v>383988</v>
+      </c>
+      <c r="B477" s="1">
+        <v>46037</v>
+      </c>
+      <c r="C477" t="s">
+        <v>580</v>
+      </c>
+      <c r="D477" t="s">
+        <v>48</v>
+      </c>
+      <c r="E477" t="s">
+        <v>39</v>
+      </c>
+      <c r="F477" t="s">
+        <v>46</v>
+      </c>
+      <c r="G477" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A478">
+        <v>275127</v>
+      </c>
+      <c r="B478" s="1">
+        <v>46044</v>
+      </c>
+      <c r="C478" t="s">
+        <v>581</v>
+      </c>
+      <c r="D478" t="s">
+        <v>16</v>
+      </c>
+      <c r="E478" t="s">
+        <v>17</v>
+      </c>
+      <c r="F478" t="s">
+        <v>18</v>
+      </c>
+      <c r="G478" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A479">
+        <v>418436</v>
+      </c>
+      <c r="B479" s="1">
+        <v>46048</v>
+      </c>
+      <c r="C479" t="s">
+        <v>582</v>
+      </c>
+      <c r="D479" t="s">
+        <v>311</v>
+      </c>
+      <c r="E479" t="s">
+        <v>30</v>
+      </c>
+      <c r="F479" t="s">
+        <v>10</v>
+      </c>
+      <c r="G479" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A480">
+        <v>420929</v>
+      </c>
+      <c r="B480" s="1">
+        <v>46051</v>
+      </c>
+      <c r="C480" t="s">
+        <v>583</v>
+      </c>
+      <c r="D480" t="s">
+        <v>271</v>
+      </c>
+      <c r="E480" t="s">
+        <v>30</v>
+      </c>
+      <c r="F480" t="s">
+        <v>14</v>
+      </c>
+      <c r="G480" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A481">
+        <v>428334</v>
+      </c>
+      <c r="B481" s="1">
+        <v>46055</v>
+      </c>
+      <c r="C481" t="s">
+        <v>584</v>
+      </c>
+      <c r="D481" t="s">
+        <v>585</v>
+      </c>
+      <c r="E481" t="s">
+        <v>51</v>
+      </c>
+      <c r="F481" t="s">
+        <v>14</v>
+      </c>
+      <c r="G481" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A482">
+        <v>428583</v>
+      </c>
+      <c r="B482" s="1">
+        <v>46055</v>
+      </c>
+      <c r="C482" t="s">
+        <v>586</v>
+      </c>
+      <c r="D482" t="s">
+        <v>13</v>
+      </c>
+      <c r="E482" t="s">
+        <v>9</v>
+      </c>
+      <c r="F482" t="s">
+        <v>18</v>
+      </c>
+      <c r="G482" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A483">
+        <v>145056</v>
+      </c>
+      <c r="B483" s="1">
+        <v>46056</v>
+      </c>
+      <c r="C483" t="s">
+        <v>587</v>
+      </c>
+      <c r="D483" t="s">
+        <v>32</v>
+      </c>
+      <c r="E483" t="s">
+        <v>9</v>
+      </c>
+      <c r="F483" t="s">
+        <v>18</v>
+      </c>
+      <c r="G483" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A484">
+        <v>428095</v>
+      </c>
+      <c r="B484" s="1">
+        <v>46057</v>
+      </c>
+      <c r="C484" t="s">
+        <v>588</v>
+      </c>
+      <c r="D484" t="s">
+        <v>13</v>
+      </c>
+      <c r="E484" t="s">
+        <v>9</v>
+      </c>
+      <c r="F484" t="s">
+        <v>18</v>
+      </c>
+      <c r="G484" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A485">
+        <v>428626</v>
+      </c>
+      <c r="B485" s="1">
+        <v>46062</v>
+      </c>
+      <c r="C485" t="s">
+        <v>589</v>
+      </c>
+      <c r="D485" t="s">
+        <v>32</v>
+      </c>
+      <c r="E485" t="s">
+        <v>9</v>
+      </c>
+      <c r="F485" t="s">
+        <v>18</v>
+      </c>
+      <c r="G485" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A486">
+        <v>425737</v>
+      </c>
+      <c r="B486" s="1">
+        <v>46069</v>
+      </c>
+      <c r="C486" t="s">
+        <v>590</v>
+      </c>
+      <c r="D486" t="s">
+        <v>13</v>
+      </c>
+      <c r="E486" t="s">
+        <v>9</v>
+      </c>
+      <c r="F486" t="s">
+        <v>18</v>
+      </c>
+      <c r="G486" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A487">
+        <v>429062</v>
+      </c>
+      <c r="B487" s="1">
+        <v>46071</v>
+      </c>
+      <c r="C487" t="s">
+        <v>591</v>
+      </c>
+      <c r="D487" t="s">
+        <v>67</v>
+      </c>
+      <c r="E487" t="s">
+        <v>39</v>
+      </c>
+      <c r="F487" t="s">
+        <v>14</v>
+      </c>
+      <c r="G487" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A488">
+        <v>301228</v>
+      </c>
+      <c r="B488" s="1">
+        <v>46072</v>
+      </c>
+      <c r="C488" t="s">
+        <v>592</v>
+      </c>
+      <c r="D488" t="s">
+        <v>24</v>
+      </c>
+      <c r="E488" t="s">
+        <v>25</v>
+      </c>
+      <c r="F488" t="s">
+        <v>46</v>
+      </c>
+      <c r="G488" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A489">
+        <v>428595</v>
+      </c>
+      <c r="B489" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C489" t="s">
+        <v>593</v>
+      </c>
+      <c r="D489" t="s">
+        <v>48</v>
+      </c>
+      <c r="E489" t="s">
+        <v>39</v>
+      </c>
+      <c r="F489" t="s">
+        <v>14</v>
+      </c>
+      <c r="G489" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
